--- a/Excel/Caja.xlsx
+++ b/Excel/Caja.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Muhia\Proyectos\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CoBoSI\Proyectos_MUHIA\Expedientes_Proy\02-GIPPro\Excel_Importacion_Masiva\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046E5B84-A231-4130-B3AC-72DD5808BC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16815" windowHeight="8340"/>
+    <workbookView xWindow="15" yWindow="45" windowWidth="9105" windowHeight="10815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Caja" sheetId="1" r:id="rId1"/>
@@ -24,19 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>kgbkj</t>
-  </si>
-  <si>
-    <t>fvdfs</t>
-  </si>
-  <si>
-    <t>xwefv</t>
-  </si>
-  <si>
-    <t>Codigo</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
   <si>
     <t>Nombre</t>
   </si>
@@ -47,19 +36,52 @@
     <t>Material</t>
   </si>
   <si>
-    <t>cesdwef</t>
-  </si>
-  <si>
-    <t>wrvs</t>
-  </si>
-  <si>
-    <t>ced</t>
+    <t>grande</t>
+  </si>
+  <si>
+    <t>madera</t>
+  </si>
+  <si>
+    <t>estándar</t>
+  </si>
+  <si>
+    <t>carton</t>
+  </si>
+  <si>
+    <t>Cajas cartón</t>
+  </si>
+  <si>
+    <t>Caja Madera</t>
+  </si>
+  <si>
+    <t>Cajas Madera</t>
+  </si>
+  <si>
+    <t>Cajas Plásticas c/tapa</t>
+  </si>
+  <si>
+    <t>Caja Plástica s/tapa</t>
+  </si>
+  <si>
+    <t>plastica</t>
+  </si>
+  <si>
+    <t>mediana</t>
+  </si>
+  <si>
+    <t>estrecha</t>
+  </si>
+  <si>
+    <t>cuadrada</t>
+  </si>
+  <si>
+    <t>chica</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -370,56 +392,113 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3">
-        <v>23</v>
+      <c r="C3" t="s">
+        <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Caja.xlsx
+++ b/Excel/Caja.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CoBoSI\Proyectos_MUHIA\Expedientes_Proy\02-GIPPro\Excel_Importacion_Masiva\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desarrollos\gippro\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046E5B84-A231-4130-B3AC-72DD5808BC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA5CE61-872B-4BE8-B4D2-F87F7F62C763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="45" windowWidth="9105" windowHeight="10815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10200" yWindow="0" windowWidth="10290" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Caja" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>Nombre</t>
   </si>
@@ -42,27 +42,9 @@
     <t>madera</t>
   </si>
   <si>
-    <t>estándar</t>
-  </si>
-  <si>
     <t>carton</t>
   </si>
   <si>
-    <t>Cajas cartón</t>
-  </si>
-  <si>
-    <t>Caja Madera</t>
-  </si>
-  <si>
-    <t>Cajas Madera</t>
-  </si>
-  <si>
-    <t>Cajas Plásticas c/tapa</t>
-  </si>
-  <si>
-    <t>Caja Plástica s/tapa</t>
-  </si>
-  <si>
     <t>plastica</t>
   </si>
   <si>
@@ -76,6 +58,33 @@
   </si>
   <si>
     <t>chica</t>
+  </si>
+  <si>
+    <t>Caja Madera Chi</t>
+  </si>
+  <si>
+    <t>Caja Madera Cu</t>
+  </si>
+  <si>
+    <t>Caja Madera Gr</t>
+  </si>
+  <si>
+    <t>Caja Madera Med</t>
+  </si>
+  <si>
+    <t>estandar</t>
+  </si>
+  <si>
+    <t>Caja Plastica s/tapa</t>
+  </si>
+  <si>
+    <t>Caja Madera Est</t>
+  </si>
+  <si>
+    <t>Caja Plastica c/tapa</t>
+  </si>
+  <si>
+    <t>Caja Carton</t>
   </si>
 </sst>
 </file>
@@ -415,21 +424,21 @@
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -437,10 +446,10 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
@@ -448,10 +457,10 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -459,7 +468,7 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
@@ -470,10 +479,10 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -481,24 +490,24 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Caja.xlsx
+++ b/Excel/Caja.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Muhia\Proyectos\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desarrollos\gippro\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA5CE61-872B-4BE8-B4D2-F87F7F62C763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16815" windowHeight="8340"/>
+    <workbookView xWindow="10200" yWindow="0" windowWidth="10290" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Caja" sheetId="1" r:id="rId1"/>
@@ -24,19 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>kgbkj</t>
-  </si>
-  <si>
-    <t>fvdfs</t>
-  </si>
-  <si>
-    <t>xwefv</t>
-  </si>
-  <si>
-    <t>Codigo</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>Nombre</t>
   </si>
@@ -47,19 +36,61 @@
     <t>Material</t>
   </si>
   <si>
-    <t>cesdwef</t>
-  </si>
-  <si>
-    <t>wrvs</t>
-  </si>
-  <si>
-    <t>ced</t>
+    <t>grande</t>
+  </si>
+  <si>
+    <t>madera</t>
+  </si>
+  <si>
+    <t>carton</t>
+  </si>
+  <si>
+    <t>plastica</t>
+  </si>
+  <si>
+    <t>mediana</t>
+  </si>
+  <si>
+    <t>estrecha</t>
+  </si>
+  <si>
+    <t>cuadrada</t>
+  </si>
+  <si>
+    <t>chica</t>
+  </si>
+  <si>
+    <t>Caja Madera Chi</t>
+  </si>
+  <si>
+    <t>Caja Madera Cu</t>
+  </si>
+  <si>
+    <t>Caja Madera Gr</t>
+  </si>
+  <si>
+    <t>Caja Madera Med</t>
+  </si>
+  <si>
+    <t>estandar</t>
+  </si>
+  <si>
+    <t>Caja Plastica s/tapa</t>
+  </si>
+  <si>
+    <t>Caja Madera Est</t>
+  </si>
+  <si>
+    <t>Caja Plastica c/tapa</t>
+  </si>
+  <si>
+    <t>Caja Carton</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -370,56 +401,113 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D6" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
